--- a/Quarter/Predicted_Jevons_Index_With_Error_Results.xlsx
+++ b/Quarter/Predicted_Jevons_Index_With_Error_Results.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Predicted_Prices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Adjacent Predicted Quarters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Model_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11673,6 +11674,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Uses_Error_Feature</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020 Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9174881104070851</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020 Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.960947447699524</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020 Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.791891930185503</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020 Q4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9446819959476075</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2021 Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>37</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2021 Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>40</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9843445311466805</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2021 Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>43</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8598609836430705</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2021 Q4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>47</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9506021244357702</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2022 Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>61</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7591946970319245</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2022 Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>67</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7421124807081474</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022 Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>71</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.7902851348544651</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2022 Q4</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>86</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7044348883994569</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2023 Q1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>92</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8172273390636386</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2023 Q2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>99</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6588804638126579</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2023 Q3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>102</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7960267823390131</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2023 Q4</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>117</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.72213845789894</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024 Q1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>121</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7681362941418085</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024 Q2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>129</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7028135326342793</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024 Q3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>128</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7933428898136806</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024 Q4</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>140</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6694605138933959</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025 Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>146</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.8205770393658314</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025 Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>133</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7602986934930194</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/Quarter/Predicted_Jevons_Index_With_Error_Results.xlsx
+++ b/Quarter/Predicted_Jevons_Index_With_Error_Results.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Predicted_Prices" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Adjacent Predicted Quarters" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Model_Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Price_Change_R2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12062,6 +12063,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Price_Change</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Samples</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2020 Q1 → 2020 Q2</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.3640508616978076</v>
+      </c>
+      <c r="C2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2020 Q2 → 2020 Q3</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.1961313831226373</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2020 Q3 → 2020 Q4</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.590300240987004</v>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020 Q4 → 2021 Q1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.05789233423561546</v>
+      </c>
+      <c r="C5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2021 Q1 → 2021 Q2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.04268716416728335</v>
+      </c>
+      <c r="C6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2021 Q2 → 2021 Q3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.02699148210375679</v>
+      </c>
+      <c r="C7" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2021 Q3 → 2021 Q4</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.05118737038481169</v>
+      </c>
+      <c r="C8" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2021 Q4 → 2022 Q1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1560751083948825</v>
+      </c>
+      <c r="C9" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2022 Q1 → 2022 Q2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.605754943778681e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2022 Q2 → 2022 Q3</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.02825473607738738</v>
+      </c>
+      <c r="C11" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2022 Q3 → 2022 Q4</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.08455082466166353</v>
+      </c>
+      <c r="C12" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2022 Q4 → 2023 Q1</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.001569110289517894</v>
+      </c>
+      <c r="C13" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2023 Q1 → 2023 Q2</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.08458835224107286</v>
+      </c>
+      <c r="C14" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2023 Q2 → 2023 Q3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.05720547099366902</v>
+      </c>
+      <c r="C15" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2023 Q3 → 2023 Q4</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.03215363851819009</v>
+      </c>
+      <c r="C16" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2023 Q4 → 2024 Q1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0003693242918264561</v>
+      </c>
+      <c r="C17" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024 Q1 → 2024 Q2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.001222538668353756</v>
+      </c>
+      <c r="C18" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024 Q2 → 2024 Q3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.001451607930053611</v>
+      </c>
+      <c r="C19" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024 Q3 → 2024 Q4</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.000235567991466179</v>
+      </c>
+      <c r="C20" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024 Q4 → 2025 Q1</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.005671711574407823</v>
+      </c>
+      <c r="C21" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025 Q1 → 2025 Q2</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.1829965400259839</v>
+      </c>
+      <c r="C22" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Overall (Average)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.0936000679003252</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1594</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
